--- a/data/satisfaction_detail/2026/1-9月/展览主承办.xlsx
+++ b/data/satisfaction_detail/2026/1-9月/展览主承办.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.470000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>9.67</v>
@@ -514,7 +514,7 @@
         <v>9.859999999999999</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>9.82</v>
+        <v>9.84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>10</v>
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9.82</v>
+        <v>9.84</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="8">
@@ -553,7 +553,7 @@
         <v>9.94</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.73</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="9">
@@ -605,7 +605,7 @@
         <v>9.619999999999999</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.74</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>9.82</v>
+        <v>9.84</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>10</v>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>9.470000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>9.93</v>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>9.44</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>9.92</v>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>9.43</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>9.94</v>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>9.41</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>9.92</v>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>9.710000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>9.83</v>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>9.68</v>
